--- a/Libraries/Vehicle/Springs/Spring/sm_car_data_Spring_AsymmetricLinear.xlsx
+++ b/Libraries/Vehicle/Springs/Spring/sm_car_data_Spring_AsymmetricLinear.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Springs\Spring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C588BB22-635B-41A5-9F4B-00F620125FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702A04DC-81A5-4731-BE2D-0ED15F71920C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="948" xr2:uid="{3D91F562-0AFF-4B18-AFD7-69ED25E9BE04}"/>
+    <workbookView xWindow="1965" yWindow="1875" windowWidth="21600" windowHeight="11295" tabRatio="948" activeTab="1" xr2:uid="{3D91F562-0AFF-4B18-AFD7-69ED25E9BE04}"/>
   </bookViews>
   <sheets>
     <sheet name="SUV_Landy_TA2PR_f" sheetId="27" r:id="rId1"/>
-    <sheet name="Sedan_HambaLG_TA2PR_r" sheetId="28" r:id="rId2"/>
+    <sheet name="SUV_Landy_TA2PRNoSteer_r" sheetId="28" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -111,7 +111,7 @@
     <t>fPreloadR</t>
   </si>
   <si>
-    <t>Sedan_HambaLG_TA2PR_AsymmetricLinear_A2</t>
+    <t>SUV_Landy_TA2PRNoSteer_AsymmetricLinear_A2</t>
   </si>
 </sst>
 </file>
@@ -981,13 +981,13 @@
         <v>12</v>
       </c>
       <c r="F5" s="18">
-        <v>1E-3</v>
+        <v>-0.02</v>
       </c>
       <c r="G5" s="18">
-        <v>0.47799999999999998</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="H5" s="18">
-        <v>0.73299999999999998</v>
+        <v>0.68300000000000005</v>
       </c>
       <c r="J5" s="13" t="s">
         <v>12</v>
@@ -1006,13 +1006,13 @@
         <v>12</v>
       </c>
       <c r="F6" s="18">
-        <v>1E-3</v>
+        <v>-0.02</v>
       </c>
       <c r="G6" s="18">
-        <v>-0.47799999999999998</v>
+        <v>-0.38800000000000001</v>
       </c>
       <c r="H6" s="18">
-        <v>0.73299999999999998</v>
+        <v>0.68300000000000005</v>
       </c>
       <c r="J6" s="13" t="s">
         <v>12</v>
@@ -1034,7 +1034,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="G7" s="18">
-        <v>0.49299999999999999</v>
+        <v>0.38300000000000001</v>
       </c>
       <c r="H7" s="18">
         <v>0.52300000000000002</v>
@@ -1059,7 +1059,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="G8" s="18">
-        <v>-0.48699999999999999</v>
+        <v>-0.38300000000000001</v>
       </c>
       <c r="H8" s="18">
         <v>0.52300000000000002</v>
